--- a/Output Data Tables/AFAT Outputs/Cost Tables/2015/Administrative_Cost_by_Airline_2015.xlsx
+++ b/Output Data Tables/AFAT Outputs/Cost Tables/2015/Administrative_Cost_by_Airline_2015.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="41" uniqueCount="41">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -169,14 +181,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
     <col min="2" max="2" width="17.7109375" customWidth="true"/>
-    <col min="3" max="3" width="11.140625" customWidth="true"/>
+    <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="19.7109375" customWidth="true"/>
-    <col min="5" max="5" width="11.140625" customWidth="true"/>
+    <col min="5" max="5" width="15.85546875" customWidth="true"/>
     <col min="6" max="6" width="12.5703125" customWidth="true"/>
     <col min="7" max="7" width="11.140625" customWidth="true"/>
     <col min="8" max="8" width="12.5703125" customWidth="true"/>
@@ -192,40 +204,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -1176,39 +1188,203 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>28827476040</v>
+      </c>
+      <c r="C25" s="0">
+        <v>17968088380</v>
+      </c>
+      <c r="D25" s="0">
+        <v>4133592770</v>
+      </c>
+      <c r="E25" s="0">
+        <v>14016708620</v>
+      </c>
+      <c r="F25" s="0">
+        <v>1676594120</v>
+      </c>
+      <c r="G25" s="0">
+        <v>4849143330</v>
+      </c>
+      <c r="H25" s="0">
+        <v>4033644630</v>
+      </c>
+      <c r="I25" s="0">
+        <v>727596840</v>
+      </c>
+      <c r="J25" s="0">
+        <v>2341765470</v>
+      </c>
+      <c r="K25" s="0">
+        <v>15642306700</v>
+      </c>
+      <c r="L25" s="0">
+        <v>78574610090</v>
+      </c>
+      <c r="M25" s="0">
+        <v>94216916790</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>10075390620</v>
+      </c>
+      <c r="C26" s="0">
+        <v>6188338670</v>
+      </c>
+      <c r="D26" s="0">
+        <v>720163860</v>
+      </c>
+      <c r="E26" s="0">
+        <v>4688478240</v>
+      </c>
+      <c r="F26" s="0">
+        <v>774712140</v>
+      </c>
+      <c r="G26" s="0">
+        <v>1596704230</v>
+      </c>
+      <c r="H26" s="0">
+        <v>1613975420</v>
+      </c>
+      <c r="I26" s="0">
+        <v>115840140</v>
+      </c>
+      <c r="J26" s="0">
+        <v>388459650</v>
+      </c>
+      <c r="K26" s="0">
+        <v>944380970</v>
+      </c>
+      <c r="L26" s="0">
+        <v>26162063840</v>
+      </c>
+      <c r="M26" s="0">
+        <v>27106444810</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>1059022060</v>
+      </c>
+      <c r="C27" s="0">
+        <v>1201359580</v>
+      </c>
+      <c r="D27" s="0">
+        <v>203971740</v>
+      </c>
+      <c r="E27" s="0">
+        <v>828950990</v>
+      </c>
+      <c r="F27" s="0">
+        <v>165763060</v>
+      </c>
+      <c r="G27" s="0">
+        <v>564402780</v>
+      </c>
+      <c r="H27" s="0">
+        <v>174825140</v>
+      </c>
+      <c r="I27" s="0">
+        <v>56938070</v>
+      </c>
+      <c r="J27" s="0">
+        <v>133291070</v>
+      </c>
+      <c r="K27" s="0">
+        <v>19020</v>
+      </c>
+      <c r="L27" s="0">
+        <v>4388524410</v>
+      </c>
+      <c r="M27" s="0">
+        <v>4388543430</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>2446829180</v>
+      </c>
+      <c r="C28" s="0">
+        <v>124706800</v>
+      </c>
+      <c r="D28" s="0">
+        <v>289999070</v>
+      </c>
+      <c r="E28" s="0">
+        <v>819358240</v>
+      </c>
+      <c r="F28" s="0">
+        <v>74492480</v>
+      </c>
+      <c r="G28" s="0">
+        <v>749228290</v>
+      </c>
+      <c r="H28" s="0">
+        <v>372744140</v>
+      </c>
+      <c r="I28" s="0">
+        <v>9849640</v>
+      </c>
+      <c r="J28" s="0">
+        <v>365899980</v>
+      </c>
+      <c r="K28" s="0">
+        <v>34690</v>
+      </c>
+      <c r="L28" s="0">
+        <v>5253102870</v>
+      </c>
+      <c r="M28" s="0">
+        <v>5253137560</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>42408717900</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>25482493430</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>5347727440</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>20353496090</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>2691561800</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>7759478630</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>6195189330</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>910224690</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>3229416170</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>16586741380</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>114378301210</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>130965042590</v>
       </c>
     </row>
